--- a/data/trans_orig/P3A_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13944</t>
+          <t>13519</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26808</t>
+          <t>27061</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6682</t>
+          <t>6558</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16046</t>
+          <t>16210</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22634</t>
+          <t>22918</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38410</t>
+          <t>38851</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,54%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53647</t>
+          <t>53394</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66511</t>
+          <t>66936</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55591</t>
+          <t>55427</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64955</t>
+          <t>65079</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>113682</t>
+          <t>113241</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>129458</t>
+          <t>129174</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>84,93%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12785</t>
+          <t>12533</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24321</t>
+          <t>24254</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18341</t>
+          <t>18217</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31163</t>
+          <t>31334</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34977</t>
+          <t>33877</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51921</t>
+          <t>51688</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>37,96%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>44366</t>
+          <t>44433</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>55902</t>
+          <t>56154</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36322</t>
+          <t>36151</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>49144</t>
+          <t>49268</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>84251</t>
+          <t>84484</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>101195</t>
+          <t>102295</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>75,12%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3417</t>
+          <t>3454</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11056</t>
+          <t>11450</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14151</t>
+          <t>13775</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26245</t>
+          <t>26355</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19401</t>
+          <t>19799</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34560</t>
+          <t>34712</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47189</t>
+          <t>46795</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54828</t>
+          <t>54791</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57699</t>
+          <t>57589</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69793</t>
+          <t>70169</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>107629</t>
+          <t>107477</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>122788</t>
+          <t>122390</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,08%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42420</t>
+          <t>42422</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60996</t>
+          <t>61022</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34989</t>
+          <t>35132</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52981</t>
+          <t>52971</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>81563</t>
+          <t>81752</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>107358</t>
+          <t>108099</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>36,05%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90300</t>
+          <t>90274</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>108876</t>
+          <t>108874</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>95581</t>
+          <t>95591</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>113573</t>
+          <t>113430</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>192500</t>
+          <t>191759</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>218295</t>
+          <t>218106</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,74%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26900</t>
+          <t>27755</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40224</t>
+          <t>40841</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37025</t>
+          <t>37638</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51259</t>
+          <t>51285</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67528</t>
+          <t>68336</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>87037</t>
+          <t>87160</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,73%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28899</t>
+          <t>28282</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42223</t>
+          <t>41368</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>33271</t>
+          <t>33245</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47505</t>
+          <t>46892</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>66615</t>
+          <t>66492</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>86124</t>
+          <t>85316</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>55,53%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42151</t>
+          <t>41751</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55786</t>
+          <t>55389</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39667</t>
+          <t>38700</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52240</t>
+          <t>52463</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>85838</t>
+          <t>86156</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>104684</t>
+          <t>104466</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>70,94%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19084</t>
+          <t>19481</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32719</t>
+          <t>33119</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20152</t>
+          <t>19929</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>32725</t>
+          <t>33692</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>42578</t>
+          <t>42796</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>61424</t>
+          <t>61106</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,5%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>160322</t>
+          <t>161367</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>195946</t>
+          <t>194835</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>172522</t>
+          <t>170832</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>206363</t>
+          <t>207188</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>343957</t>
+          <t>343905</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>392820</t>
+          <t>391851</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,0%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>306729</t>
+          <t>307840</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>342353</t>
+          <t>341308</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>322186</t>
+          <t>321361</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>356027</t>
+          <t>357717</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>638405</t>
+          <t>639374</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>687268</t>
+          <t>687320</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7355</t>
+          <t>7500</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17002</t>
+          <t>17258</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7497</t>
+          <t>7745</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18383</t>
+          <t>18205</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17373</t>
+          <t>17370</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31979</t>
+          <t>32089</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,83%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44219</t>
+          <t>43963</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53866</t>
+          <t>53721</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55027</t>
+          <t>55205</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65913</t>
+          <t>65665</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>102652</t>
+          <t>102542</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>117258</t>
+          <t>117261</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12318</t>
+          <t>11823</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24083</t>
+          <t>23953</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15537</t>
+          <t>15777</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28050</t>
+          <t>28460</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31102</t>
+          <t>30836</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47862</t>
+          <t>47658</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,59%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>41296</t>
+          <t>41426</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>53061</t>
+          <t>53556</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40476</t>
+          <t>40066</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>52989</t>
+          <t>52749</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>86043</t>
+          <t>86247</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>102803</t>
+          <t>103069</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,97%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9489</t>
+          <t>9840</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20317</t>
+          <t>20436</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8634</t>
+          <t>8551</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20055</t>
+          <t>19284</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20785</t>
+          <t>21335</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36455</t>
+          <t>36548</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,18%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46206</t>
+          <t>46087</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57034</t>
+          <t>56683</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47909</t>
+          <t>48680</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59330</t>
+          <t>59413</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>98032</t>
+          <t>97939</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>113702</t>
+          <t>113152</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,14%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38428</t>
+          <t>38502</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57135</t>
+          <t>57108</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37902</t>
+          <t>37983</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58190</t>
+          <t>57636</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>81241</t>
+          <t>82194</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>107323</t>
+          <t>108703</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,5%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>79345</t>
+          <t>79372</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>98052</t>
+          <t>97978</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>103174</t>
+          <t>103728</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>123462</t>
+          <t>123381</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>190521</t>
+          <t>189141</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>216603</t>
+          <t>215650</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>72,4%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30284</t>
+          <t>30508</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46516</t>
+          <t>46005</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40728</t>
+          <t>40427</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56859</t>
+          <t>56438</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>75370</t>
+          <t>75680</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>98243</t>
+          <t>98082</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>52,89%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46935</t>
+          <t>47446</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>63167</t>
+          <t>62943</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35149</t>
+          <t>35570</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51280</t>
+          <t>51581</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>87216</t>
+          <t>87377</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>110089</t>
+          <t>109779</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,19%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28608</t>
+          <t>27744</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40248</t>
+          <t>40417</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30483</t>
+          <t>30950</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>44343</t>
+          <t>44511</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>62313</t>
+          <t>62557</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81373</t>
+          <t>80606</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,0%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13663</t>
+          <t>13494</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25303</t>
+          <t>26167</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29695</t>
+          <t>29527</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43555</t>
+          <t>43088</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>46576</t>
+          <t>47343</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>65636</t>
+          <t>65392</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>51,11%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>146023</t>
+          <t>148578</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>180617</t>
+          <t>181319</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>164037</t>
+          <t>161831</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>198568</t>
+          <t>198110</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>320438</t>
+          <t>321149</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>368067</t>
+          <t>367570</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,24%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>296348</t>
+          <t>295646</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>330942</t>
+          <t>328387</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>338742</t>
+          <t>339200</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>373273</t>
+          <t>375479</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>646208</t>
+          <t>646705</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>693837</t>
+          <t>693126</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>68,34%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10242</t>
+          <t>10778</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21782</t>
+          <t>22813</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15066</t>
+          <t>14591</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28197</t>
+          <t>28828</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28411</t>
+          <t>28311</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45412</t>
+          <t>45091</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,51%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43049</t>
+          <t>42018</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54589</t>
+          <t>54053</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50057</t>
+          <t>49426</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63188</t>
+          <t>63663</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>97673</t>
+          <t>97994</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>114674</t>
+          <t>114774</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,21%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20105</t>
+          <t>20309</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33557</t>
+          <t>34230</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25421</t>
+          <t>25253</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39636</t>
+          <t>39985</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49655</t>
+          <t>49126</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69269</t>
+          <t>68824</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,24%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48754</t>
+          <t>48081</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>62206</t>
+          <t>62002</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53431</t>
+          <t>53082</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>67646</t>
+          <t>67814</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>106109</t>
+          <t>106554</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>125723</t>
+          <t>126252</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,99%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13259</t>
+          <t>13369</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5675</t>
+          <t>5751</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15591</t>
+          <t>15382</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12350</t>
+          <t>12547</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25274</t>
+          <t>25226</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,88%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35965</t>
+          <t>35855</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44782</t>
+          <t>44536</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45420</t>
+          <t>45629</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55336</t>
+          <t>55260</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>84960</t>
+          <t>85008</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>97884</t>
+          <t>97687</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,62%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46352</t>
+          <t>45258</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65430</t>
+          <t>65227</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41446</t>
+          <t>41474</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61719</t>
+          <t>60468</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>93470</t>
+          <t>93439</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>121175</t>
+          <t>120838</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>35,89%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>100367</t>
+          <t>100570</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>119445</t>
+          <t>120539</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>109164</t>
+          <t>110415</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>129437</t>
+          <t>129409</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>215505</t>
+          <t>215842</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>243210</t>
+          <t>243241</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,25%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31502</t>
+          <t>30747</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47316</t>
+          <t>47373</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35927</t>
+          <t>36329</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52701</t>
+          <t>53066</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71216</t>
+          <t>71259</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>94271</t>
+          <t>93805</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>46,73%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>54263</t>
+          <t>54206</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>70077</t>
+          <t>70832</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46452</t>
+          <t>46087</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63226</t>
+          <t>62824</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>106461</t>
+          <t>106927</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>129516</t>
+          <t>129473</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>53,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,5%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19806</t>
+          <t>20532</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32335</t>
+          <t>32416</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23796</t>
+          <t>23902</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37765</t>
+          <t>37645</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>47571</t>
+          <t>47691</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>66124</t>
+          <t>66735</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>52,07%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>27999</t>
+          <t>27918</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>40528</t>
+          <t>39802</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30060</t>
+          <t>30180</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>44029</t>
+          <t>43923</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>62035</t>
+          <t>61424</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>80588</t>
+          <t>80468</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>62,79%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>154008</t>
+          <t>153190</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>187285</t>
+          <t>187269</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>171398</t>
+          <t>168905</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>206715</t>
+          <t>206654</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>332007</t>
+          <t>334985</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>385208</t>
+          <t>388354</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,49%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>336791</t>
+          <t>336807</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>370068</t>
+          <t>370886</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>363477</t>
+          <t>363538</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>398794</t>
+          <t>401287</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>709060</t>
+          <t>705914</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>762261</t>
+          <t>759283</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>69,39%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>88463</t>
+          <t>88036</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>98285</t>
+          <t>98293</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>113419</t>
+          <t>113895</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>127314</t>
+          <t>127313</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>205836</t>
+          <t>205166</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>223209</t>
+          <t>222729</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,28%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6177</t>
+          <t>6169</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15999</t>
+          <t>16426</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>9595</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23489</t>
+          <t>23013</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18161</t>
+          <t>18641</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35534</t>
+          <t>36204</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>78270</t>
+          <t>79721</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89086</t>
+          <t>89104</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>80930</t>
+          <t>80511</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>90370</t>
+          <t>90269</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>163823</t>
+          <t>163523</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>178006</t>
+          <t>177602</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,35%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5595</t>
+          <t>5577</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16411</t>
+          <t>14960</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5203</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14643</t>
+          <t>15062</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12248</t>
+          <t>12652</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>26431</t>
+          <t>26731</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32126</t>
+          <t>31725</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43058</t>
+          <t>42905</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40899</t>
+          <t>40386</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54822</t>
+          <t>54473</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>78372</t>
+          <t>77994</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>95555</t>
+          <t>95476</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,51%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8803</t>
+          <t>8956</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19735</t>
+          <t>20136</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9031</t>
+          <t>9380</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22954</t>
+          <t>23467</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20159</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>37342</t>
+          <t>37720</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,6%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>163356</t>
+          <t>163053</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>195352</t>
+          <t>195570</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>181297</t>
+          <t>182370</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>199604</t>
+          <t>200048</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>353341</t>
+          <t>353478</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>390167</t>
+          <t>389021</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,0%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23473</t>
+          <t>23255</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55469</t>
+          <t>55772</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18668</t>
+          <t>18224</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36975</t>
+          <t>35902</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>46930</t>
+          <t>48076</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>83756</t>
+          <t>83619</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>100301</t>
+          <t>101602</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>112008</t>
+          <t>112507</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>127798</t>
+          <t>128050</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>145410</t>
+          <t>145172</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>232838</t>
+          <t>234331</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>254380</t>
+          <t>254727</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,31%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7420</t>
+          <t>6921</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19127</t>
+          <t>17826</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17207</t>
+          <t>17445</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34819</t>
+          <t>34567</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27665</t>
+          <t>27318</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49207</t>
+          <t>47714</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53416</t>
+          <t>52524</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>63137</t>
+          <t>62754</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>55491</t>
+          <t>54905</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>66382</t>
+          <t>66241</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>111381</t>
+          <t>111429</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>126622</t>
+          <t>127041</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>90,16%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5758</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15479</t>
+          <t>16371</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5621</t>
+          <t>5762</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16512</t>
+          <t>17098</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14276</t>
+          <t>13857</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>29517</t>
+          <t>29469</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>544312</t>
+          <t>542711</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>582696</t>
+          <t>582449</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>630431</t>
+          <t>628852</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>664457</t>
+          <t>663625</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,47 +10746,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>83,93%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>88,57%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1630</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>1213073</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>1184200</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>1237576</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>86,19%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>84,14%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>88,69%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1630</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1213073</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>1187100</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>1240477</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>86,19%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>84,35%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>87,93%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>75457</t>
+          <t>75704</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>113841</t>
+          <t>115442</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>84768</t>
+          <t>85600</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>118794</t>
+          <t>120373</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,47 +10859,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
+          <t>16,07%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>194305</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>169802</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>223178</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>13,81%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>12,07%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
           <t>15,86%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>194305</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>166901</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>220278</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>13,81%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>11,86%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>15,65%</t>
         </is>
       </c>
     </row>
